--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>7.7</v>
       </c>
       <c r="M20" t="n">
-        <v>2.95</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>3.65</v>
+        <v>1.38</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.63</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7.7</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>2.95</v>
       </c>
       <c r="N22" t="n">
-        <v>1.38</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AI29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.7</v>
+        <v>2.15</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>1.38</v>
+        <v>3.65</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N21" t="n">
         <v>3.65</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>7.7</v>
       </c>
       <c r="M22" t="n">
-        <v>2.95</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>3.65</v>
+        <v>1.38</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB22" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.63</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3584,6 +3584,363 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
+        <v>46029.875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>El Bayadh</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ES Mostaganem</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3" t="n">
+        <v>46029.875</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>MC Oran</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3" t="n">
+        <v>46029.875</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ben Aknoun</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Oued Akbou</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="n">
         <v>46029.875</v>
       </c>
     </row>

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.15</v>
+        <v>7.7</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>3.65</v>
+        <v>1.38</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7.7</v>
+        <v>2.15</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>1.38</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI29"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46029.47916666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,10 +1531,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46029.5625</v>
@@ -1849,49 +1849,49 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AA12" t="n">
         <v>2.05</v>
@@ -1900,22 +1900,22 @@
         <v>1.77</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.7</v>
+        <v>2.13</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>3.11</v>
       </c>
       <c r="N20" t="n">
-        <v>1.38</v>
+        <v>3.59</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>7.3</v>
       </c>
       <c r="M21" t="n">
-        <v>2.95</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
-        <v>3.65</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB21" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="N22" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46029.71875</v>
+        <v>46029.70833333334</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46029.71875</v>
+        <v>46029.70833333334</v>
       </c>
     </row>
     <row r="25">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,76 +3396,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46029.8125</v>
+        <v>46029.71875</v>
       </c>
     </row>
     <row r="26">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,76 +3515,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46029.875</v>
+        <v>46029.71875</v>
       </c>
     </row>
     <row r="27">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3941,6 +3941,125 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
+        <v>46029.875</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>El Bayadh</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ES Mostaganem</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3" t="n">
         <v>46029.875</v>
       </c>
     </row>

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2.7</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V14" t="n">
-        <v>8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.56</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.03</v>
+        <v>1.57</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>7.4</v>
+        <v>2.08</v>
       </c>
       <c r="O16" t="n">
-        <v>1.9</v>
+        <v>3.42</v>
       </c>
       <c r="P16" t="n">
-        <v>2.48</v>
+        <v>2.19</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.25</v>
+        <v>2.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.84</v>
+        <v>3.23</v>
       </c>
       <c r="T16" t="n">
-        <v>2.16</v>
+        <v>2.63</v>
       </c>
       <c r="U16" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.81</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
         <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.13</v>
+        <v>1.77</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.05</v>
+        <v>1.3</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.45</v>
+        <v>1.88</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.08</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.42</v>
+        <v>2.39</v>
       </c>
       <c r="P17" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>3.23</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.63</v>
+        <v>2.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.77</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>2.04</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.39</v>
+        <v>1.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>3.84</v>
       </c>
       <c r="T18" t="n">
-        <v>2.94</v>
+        <v>2.16</v>
       </c>
       <c r="U18" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="V18" t="n">
+        <v>4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z18" t="n">
         <v>6.5</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AA18" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>2.81</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.34</v>
+        <v>2.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.04</v>
+        <v>3.05</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.7</v>
+        <v>3.56</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>2.03</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.13</v>
+        <v>7.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.11</v>
+        <v>4.8</v>
       </c>
       <c r="N20" t="n">
-        <v>3.59</v>
+        <v>1.38</v>
       </c>
       <c r="O20" t="n">
-        <v>2.96</v>
+        <v>7.39</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>1.89</v>
       </c>
       <c r="R20" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>2.53</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>8.199999999999999</v>
+        <v>5.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.76</v>
+        <v>2.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AE20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF20" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7.3</v>
+        <v>2.13</v>
       </c>
       <c r="M21" t="n">
-        <v>4.8</v>
+        <v>3.11</v>
       </c>
       <c r="N21" t="n">
-        <v>1.38</v>
+        <v>3.59</v>
       </c>
       <c r="O21" t="n">
-        <v>7.39</v>
+        <v>2.96</v>
       </c>
       <c r="P21" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.89</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="U21" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>5.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.55</v>
+        <v>3.76</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1025,13 +1025,13 @@
         <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>3.58</v>
+        <v>3.53</v>
       </c>
       <c r="P5" t="n">
         <v>2.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
@@ -1052,7 +1052,7 @@
         <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
         <v>1.16</v>
@@ -1067,22 +1067,22 @@
         <v>2.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="AG5" t="n">
         <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46029.47916666666</v>
@@ -1623,10 +1623,10 @@
         <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R10" t="n">
         <v>1.16</v>
@@ -1635,10 +1635,10 @@
         <v>4.05</v>
       </c>
       <c r="T10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V10" t="n">
         <v>4</v>
@@ -1653,7 +1653,7 @@
         <v>1.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AA10" t="n">
         <v>1.31</v>
@@ -1677,7 +1677,7 @@
         <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46029.5625</v>
@@ -1864,25 +1864,25 @@
         <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1.05</v>
@@ -1891,7 +1891,7 @@
         <v>1.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.31</v>
+        <v>3.12</v>
       </c>
       <c r="AA12" t="n">
         <v>2.05</v>
@@ -1900,7 +1900,7 @@
         <v>1.77</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD12" t="n">
         <v>1.26</v>
@@ -1912,10 +1912,10 @@
         <v>1.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1989,25 +1989,25 @@
         <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="T13" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V13" t="n">
         <v>7.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
         <v>3.44</v>
@@ -2022,7 +2022,7 @@
         <v>3.16</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
         <v>1.68</v>
@@ -2031,10 +2031,10 @@
         <v>2.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.3</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z14" t="n">
-        <v>4.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>5.47</v>
       </c>
       <c r="N15" t="n">
-        <v>2.65</v>
+        <v>7.22</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>1.82</v>
       </c>
       <c r="P15" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.04</v>
+        <v>6.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="S15" t="n">
-        <v>2.93</v>
+        <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="U15" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="V15" t="n">
-        <v>6.25</v>
+        <v>4.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.4</v>
+        <v>5.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.34</v>
+        <v>2.09</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.46</v>
+        <v>3.05</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.45</v>
+        <v>2.13</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N16" t="n">
-        <v>2.08</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
-        <v>3.42</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.6</v>
+        <v>4.03</v>
       </c>
       <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.3</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>1.79</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="O17" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Q17" t="n">
         <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="T17" t="n">
-        <v>2.94</v>
+        <v>3.16</v>
       </c>
       <c r="U17" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.34</v>
+        <v>3.56</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>7.4</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.9</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AB18" t="n">
-        <v>2.81</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.05</v>
+        <v>1.43</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>3.45</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>5.4</v>
+        <v>2.08</v>
       </c>
       <c r="O19" t="n">
-        <v>2.38</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>2.67</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.36</v>
       </c>
-      <c r="V19" t="n">
-        <v>8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE19" t="n">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.08</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2813,7 +2813,7 @@
         <v>7.39</v>
       </c>
       <c r="P20" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="Q20" t="n">
         <v>1.89</v>
@@ -2822,22 +2822,22 @@
         <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="U20" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
         <v>1.16</v>
@@ -2855,7 +2855,7 @@
         <v>2.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE20" t="n">
         <v>1.83</v>
@@ -2864,10 +2864,10 @@
         <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="M21" t="n">
-        <v>3.11</v>
+        <v>2.91</v>
       </c>
       <c r="N21" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG21" t="n">
         <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,70 +3039,70 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="M22" t="n">
-        <v>2.91</v>
+        <v>3.11</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="O22" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="T22" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>9.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.77</v>
+        <v>3.07</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="AD22" t="n">
         <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AH22" t="n">
         <v>1.65</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.69</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>1.73</v>
       </c>
       <c r="O25" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q25" t="n">
         <v>2.25</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5</v>
       </c>
       <c r="R25" t="n">
         <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="T25" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U25" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>6.35</v>
+        <v>6.1</v>
       </c>
       <c r="W25" t="n">
         <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.18</v>
+        <v>1.23</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46029.71875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>1.73</v>
+        <v>4.55</v>
       </c>
       <c r="O26" t="n">
-        <v>4.9</v>
+        <v>2.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
         <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="T26" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="V26" t="n">
-        <v>6.1</v>
+        <v>6.35</v>
       </c>
       <c r="W26" t="n">
         <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z26" t="n">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.16</v>
+        <v>1.18</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.23</v>
+        <v>2.1</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46029.71875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.41</v>
+        <v>2.69</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4</v>
+        <v>3.41</v>
       </c>
       <c r="N12" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V12" t="n">
         <v>7.4</v>
       </c>
-      <c r="O12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>3.16</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.54</v>
+        <v>1.68</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.5</v>
+        <v>2.08</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.87</v>
+        <v>1.49</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.69</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>3.41</v>
+        <v>4.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.47</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.02</v>
+        <v>1.97</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>8.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="U13" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.44</v>
+        <v>3.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.16</v>
+        <v>3.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.68</v>
+        <v>2.54</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.08</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.49</v>
+        <v>2.87</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.88</v>
+        <v>3.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>2.08</v>
       </c>
       <c r="O14" t="n">
-        <v>2.39</v>
+        <v>3.9</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>2.67</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="T14" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.04</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>2.39</v>
       </c>
       <c r="P18" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.98</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="U18" t="n">
         <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.73</v>
+        <v>3.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.43</v>
+        <v>2.04</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M19" t="n">
         <v>3.45</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.55</v>
-      </c>
       <c r="N19" t="n">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.67</v>
+        <v>2.98</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.1</v>
+        <v>3.73</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.3</v>
+        <v>2.26</v>
       </c>
       <c r="M20" t="n">
-        <v>4.8</v>
+        <v>2.91</v>
       </c>
       <c r="N20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.38</v>
       </c>
-      <c r="O20" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z20" t="n">
-        <v>4.33</v>
+        <v>2.77</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.26</v>
+        <v>7.3</v>
       </c>
       <c r="M21" t="n">
-        <v>2.91</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
-        <v>3.02</v>
+        <v>7.39</v>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.25</v>
+        <v>1.89</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="V21" t="n">
-        <v>9.5</v>
+        <v>5.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.77</v>
+        <v>4.33</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB21" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AC21" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.65</v>
+        <v>1.08</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.45</v>
+        <v>1.88</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.08</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.9</v>
+        <v>2.39</v>
       </c>
       <c r="P14" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="U14" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>2.04</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.13</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="O16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.5</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="U16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.33</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG16" t="n">
+      <c r="AH16" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.79</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.67</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="AF17" t="n">
         <v>2.07</v>
       </c>
-      <c r="Q17" t="n">
-        <v>5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>8</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.08</v>
+        <v>1.43</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="O18" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>4.03</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.99</v>
+        <v>2.4</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z18" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.65</v>
+        <v>5.4</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.98</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.73</v>
+        <v>3.04</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.43</v>
+        <v>2.08</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.26</v>
+        <v>7.3</v>
       </c>
       <c r="M20" t="n">
-        <v>2.91</v>
+        <v>4.8</v>
       </c>
       <c r="N20" t="n">
-        <v>3.5</v>
+        <v>1.38</v>
       </c>
       <c r="O20" t="n">
-        <v>3.02</v>
+        <v>7.39</v>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.25</v>
+        <v>1.89</v>
       </c>
       <c r="R20" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>9.5</v>
+        <v>5.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.77</v>
+        <v>4.33</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AC20" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.65</v>
+        <v>1.08</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7.3</v>
+        <v>2.26</v>
       </c>
       <c r="M21" t="n">
-        <v>4.8</v>
+        <v>2.91</v>
       </c>
       <c r="N21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.38</v>
       </c>
-      <c r="O21" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z21" t="n">
-        <v>4.33</v>
+        <v>2.77</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>1.73</v>
+        <v>4.55</v>
       </c>
       <c r="O25" t="n">
-        <v>4.95</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
         <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="T25" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V25" t="n">
-        <v>6.1</v>
+        <v>6.35</v>
       </c>
       <c r="W25" t="n">
         <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z25" t="n">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AF25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH25" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.23</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46029.71875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>4.55</v>
+        <v>1.73</v>
       </c>
       <c r="O26" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q26" t="n">
         <v>2.25</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>5</v>
       </c>
       <c r="R26" t="n">
         <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>6.35</v>
+        <v>6.1</v>
       </c>
       <c r="W26" t="n">
         <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.18</v>
+        <v>2.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.1</v>
+        <v>1.23</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46029.71875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
         <v>2.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46029.47916666666</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>2.75</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P10" t="n">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="Q10" t="n">
         <v>2.66</v>
@@ -1674,10 +1674,10 @@
         <v>3.16</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46029.5625</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.69</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
-        <v>3.41</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.47</v>
+        <v>7.4</v>
       </c>
       <c r="O12" t="n">
-        <v>3.02</v>
+        <v>1.9</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH12" t="n">
         <v>3.1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.49</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>2.69</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4</v>
+        <v>3.41</v>
       </c>
       <c r="N13" t="n">
-        <v>7.4</v>
+        <v>2.47</v>
       </c>
       <c r="O13" t="n">
-        <v>1.97</v>
+        <v>3.02</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.4</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="T13" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.54</v>
+        <v>1.69</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.87</v>
+        <v>1.49</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Q14" t="n">
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.81</v>
+        <v>2.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.44</v>
+        <v>2.13</v>
       </c>
       <c r="M15" t="n">
-        <v>5.47</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
-        <v>7.22</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.25</v>
+        <v>3.82</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2.15</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.09</v>
+        <v>2.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.05</v>
+        <v>1.74</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M16" t="n">
         <v>3.45</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.55</v>
-      </c>
       <c r="N16" t="n">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.67</v>
+        <v>2.95</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.1</v>
+        <v>3.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>1.37</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>7.22</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>1.82</v>
       </c>
       <c r="P17" t="n">
-        <v>2.11</v>
+        <v>2.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.98</v>
+        <v>6.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB17" t="n">
         <v>2.8</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AC17" t="n">
-        <v>3.3</v>
+        <v>2.09</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.43</v>
+        <v>3.05</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.03</v>
+        <v>4.17</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4</v>
+        <v>2.99</v>
       </c>
       <c r="U18" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.7</v>
+        <v>3.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>3.45</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>5.4</v>
+        <v>2.08</v>
       </c>
       <c r="O19" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>2.66</v>
       </c>
       <c r="R19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.47</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.36</v>
       </c>
-      <c r="V19" t="n">
-        <v>8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE19" t="n">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="AG19" t="n">
         <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.08</v>
+        <v>1.27</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.3</v>
+        <v>2.13</v>
       </c>
       <c r="M20" t="n">
-        <v>4.8</v>
+        <v>3.11</v>
       </c>
       <c r="N20" t="n">
-        <v>1.38</v>
+        <v>3.59</v>
       </c>
       <c r="O20" t="n">
-        <v>7.39</v>
+        <v>3.02</v>
       </c>
       <c r="P20" t="n">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.89</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.55</v>
+        <v>3.76</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.83</v>
       </c>
-      <c r="AF20" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2929,19 +2929,19 @@
         <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="P21" t="n">
         <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="R21" t="n">
         <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>2.47</v>
+        <v>2.67</v>
       </c>
       <c r="T21" t="n">
         <v>3.4</v>
@@ -2977,13 +2977,13 @@
         <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AH21" t="n">
         <v>1.65</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.13</v>
+        <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.11</v>
+        <v>4.8</v>
       </c>
       <c r="N22" t="n">
-        <v>3.59</v>
+        <v>1.38</v>
       </c>
       <c r="O22" t="n">
-        <v>2.96</v>
+        <v>7.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>1.89</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="V22" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.07</v>
+        <v>4.33</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.76</v>
+        <v>2.55</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.65</v>
+        <v>1.07</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3399,16 +3399,16 @@
         <v>1.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="O25" t="n">
         <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
         <v>5</v>
@@ -3417,7 +3417,7 @@
         <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>2.98</v>
+        <v>3.21</v>
       </c>
       <c r="T25" t="n">
         <v>2.5</v>
@@ -3429,7 +3429,7 @@
         <v>6.35</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
         <v>1.05</v>
@@ -3450,13 +3450,13 @@
         <v>2.88</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AG25" t="n">
         <v>1.18</v>
@@ -3527,7 +3527,7 @@
         <v>4.95</v>
       </c>
       <c r="P26" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="Q26" t="n">
         <v>2.25</v>
@@ -3545,7 +3545,7 @@
         <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="W26" t="n">
         <v>1.09</v>
@@ -3572,16 +3572,16 @@
         <v>1.43</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46029.71875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.41</v>
+        <v>2.69</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4</v>
+        <v>3.41</v>
       </c>
       <c r="N12" t="n">
-        <v>7.4</v>
+        <v>2.47</v>
       </c>
       <c r="O12" t="n">
-        <v>1.9</v>
+        <v>3.02</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.4</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="T12" t="n">
-        <v>3.13</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.39</v>
+        <v>1.69</v>
       </c>
       <c r="AF12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.52</v>
       </c>
-      <c r="AG12" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH12" t="n">
-        <v>3.1</v>
+        <v>1.49</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.69</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>3.41</v>
+        <v>4.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.47</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.02</v>
+        <v>1.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>8.4</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.69</v>
+        <v>2.39</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.07</v>
+        <v>1.52</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.49</v>
+        <v>3.1</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>4.33</v>
       </c>
       <c r="O14" t="n">
         <v>2.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.04</v>
+        <v>3.41</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N15" t="n">
         <v>2.13</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.1</v>
-      </c>
       <c r="O15" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.5</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.45</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="W15" t="n">
         <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.65</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>2.39</v>
       </c>
       <c r="P16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.09</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.4</v>
+        <v>2.09</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="M17" t="n">
-        <v>5.6</v>
+        <v>3.56</v>
       </c>
       <c r="N17" t="n">
-        <v>7.22</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.25</v>
+        <v>3.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.84</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="V17" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.09</v>
+        <v>2.81</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.05</v>
+        <v>1.76</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.88</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O18" t="n">
         <v>3.4</v>
       </c>
-      <c r="N18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.39</v>
-      </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.17</v>
+        <v>2.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T18" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
         <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.14</v>
+        <v>3.77</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.04</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.45</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.08</v>
+        <v>7.15</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>1.82</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.66</v>
+        <v>6.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>3.12</v>
+        <v>3.84</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="U19" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="V19" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AE19" t="n">
         <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.27</v>
+        <v>3.05</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,70 +2801,70 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="M20" t="n">
-        <v>3.11</v>
+        <v>2.91</v>
       </c>
       <c r="N20" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AH20" t="n">
         <v>1.65</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,70 +2920,70 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="M21" t="n">
-        <v>2.91</v>
+        <v>3.11</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="O21" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>9.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
         <v>1.65</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3396,19 +3396,19 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M25" t="n">
         <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="O25" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="Q25" t="n">
         <v>5</v>
@@ -3417,28 +3417,28 @@
         <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
         <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>6.35</v>
+        <v>6.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
         <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="AA25" t="n">
         <v>1.8</v>
@@ -3447,10 +3447,10 @@
         <v>1.95</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE25" t="n">
         <v>1.77</v>
@@ -3515,22 +3515,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
         <v>1.73</v>
       </c>
       <c r="O26" t="n">
-        <v>4.95</v>
+        <v>4.85</v>
       </c>
       <c r="P26" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R26" t="n">
         <v>1.35</v>
@@ -3542,13 +3542,13 @@
         <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V26" t="n">
         <v>6.15</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
         <v>1.04</v>
@@ -3560,25 +3560,25 @@
         <v>4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
         <v>2.68</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="n">
         <v>1.22</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1849,19 +1849,19 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="M12" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
         <v>3.02</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
         <v>3.1</v>
@@ -1870,40 +1870,40 @@
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="T12" t="n">
         <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
         <v>3.44</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>3.22</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
         <v>1.69</v>
@@ -1915,7 +1915,7 @@
         <v>1.52</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="O13" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="P13" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="U13" t="n">
         <v>1.37</v>
@@ -2007,34 +2007,34 @@
         <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.82</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.95</v>
+        <v>2.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="T14" t="n">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="M17" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>4.95</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>3.03</v>
       </c>
       <c r="U17" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="V17" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>3.41</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.81</v>
+        <v>3.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>7.15</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>1.82</v>
       </c>
       <c r="P18" t="n">
-        <v>2.11</v>
+        <v>2.64</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.92</v>
+        <v>6.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>2.85</v>
+        <v>3.84</v>
       </c>
       <c r="T18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB18" t="n">
         <v>2.75</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AC18" t="n">
-        <v>3.35</v>
+        <v>2.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.38</v>
       </c>
-      <c r="M19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N19" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.05</v>
+        <v>1.76</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2801,28 +2801,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="M20" t="n">
-        <v>2.91</v>
+        <v>2.99</v>
       </c>
       <c r="N20" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="P20" t="n">
         <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="R20" t="n">
         <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="T20" t="n">
         <v>3.4</v>
@@ -2831,7 +2831,7 @@
         <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
         <v>1.06</v>
@@ -2840,7 +2840,7 @@
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z20" t="n">
         <v>2.77</v>
@@ -2849,7 +2849,7 @@
         <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC20" t="n">
         <v>4.2</v>
@@ -2858,16 +2858,16 @@
         <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
         <v>1.41</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2920,16 +2920,16 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.13</v>
+        <v>2.42</v>
       </c>
       <c r="M21" t="n">
-        <v>3.11</v>
+        <v>3.02</v>
       </c>
       <c r="N21" t="n">
-        <v>3.59</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="P21" t="n">
         <v>2.05</v>
@@ -2938,10 +2938,10 @@
         <v>3.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T21" t="n">
         <v>2.9</v>
@@ -2953,40 +2953,40 @@
         <v>8.199999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
         <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.76</v>
+        <v>3.95</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AF21" t="n">
         <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7.3</v>
+        <v>7.84</v>
       </c>
       <c r="M22" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="O22" t="n">
-        <v>7.4</v>
+        <v>7.72</v>
       </c>
       <c r="P22" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R22" t="n">
         <v>1.31</v>
@@ -3063,31 +3063,31 @@
         <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="U22" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V22" t="n">
         <v>5.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA22" t="n">
         <v>1.62</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AC22" t="n">
         <v>2.55</v>
@@ -3096,13 +3096,13 @@
         <v>1.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
         <v>1.07</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.56</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
-        <v>3.02</v>
+        <v>1.86</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.06</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
         <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.69</v>
+        <v>2.58</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>3.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>2.56</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.86</v>
+        <v>3.02</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.699999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
       </c>
       <c r="S13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.88</v>
       </c>
-      <c r="T13" t="n">
-        <v>3.05</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="V13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
         <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.58</v>
+        <v>1.69</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.24</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>1.82</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.92</v>
+        <v>4.95</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.77</v>
+        <v>3.41</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.81</v>
       </c>
-      <c r="T16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V16" t="n">
-        <v>8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.56</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.09</v>
+        <v>1.76</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.82</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.95</v>
+        <v>2.92</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="T17" t="n">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="M18" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>7.15</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.82</v>
+        <v>2.39</v>
       </c>
       <c r="P18" t="n">
-        <v>2.64</v>
+        <v>2.07</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>3.84</v>
+        <v>2.81</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.44</v>
+        <v>2.09</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.1</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.81</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.76</v>
+        <v>3.05</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="O20" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.32</v>
       </c>
-      <c r="M20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AC20" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.64</v>
+        <v>1.07</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,64 +2920,64 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="M21" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AF21" t="n">
         <v>1.83</v>
@@ -2986,7 +2986,7 @@
         <v>1.41</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7.84</v>
+        <v>2.42</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>3.02</v>
       </c>
       <c r="N22" t="n">
-        <v>1.39</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>7.72</v>
+        <v>3.12</v>
       </c>
       <c r="P22" t="n">
-        <v>2.64</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.87</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.62</v>
+        <v>2.34</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.32</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.55</v>
+        <v>3.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.07</v>
+        <v>1.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.67</v>
+        <v>4.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>4.8</v>
+        <v>1.73</v>
       </c>
       <c r="O25" t="n">
-        <v>2.24</v>
+        <v>4.85</v>
       </c>
       <c r="P25" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="R25" t="n">
         <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="T25" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V25" t="n">
-        <v>6.3</v>
+        <v>6.15</v>
       </c>
       <c r="W25" t="n">
         <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46029.71875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.5</v>
+        <v>1.67</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>1.73</v>
+        <v>4.8</v>
       </c>
       <c r="O26" t="n">
-        <v>4.85</v>
+        <v>2.24</v>
       </c>
       <c r="P26" t="n">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
         <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>6.15</v>
+        <v>6.3</v>
       </c>
       <c r="W26" t="n">
         <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z26" t="n">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH26" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46029.71875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>2.56</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.86</v>
+        <v>3.02</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.699999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.88</v>
       </c>
-      <c r="T12" t="n">
-        <v>3.05</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
         <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.58</v>
+        <v>1.69</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.24</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.56</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="O13" t="n">
-        <v>3.02</v>
+        <v>1.86</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="U13" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.06</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
         <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.69</v>
+        <v>2.58</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>3.24</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="M16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.56</v>
       </c>
-      <c r="N16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.81</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="T17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2.3</v>
       </c>
-      <c r="O17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>2.39</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>2.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.1</v>
+        <v>3.77</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.09</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.84</v>
+        <v>2.42</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>3.02</v>
       </c>
       <c r="N20" t="n">
-        <v>1.39</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>7.72</v>
+        <v>3.12</v>
       </c>
       <c r="P20" t="n">
-        <v>2.64</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.87</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.62</v>
+        <v>2.34</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.32</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.55</v>
+        <v>3.95</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.07</v>
+        <v>1.6</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.42</v>
+        <v>7.84</v>
       </c>
       <c r="M22" t="n">
-        <v>3.02</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>1.39</v>
       </c>
       <c r="O22" t="n">
-        <v>3.12</v>
+        <v>7.72</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.64</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>1.87</v>
       </c>
       <c r="R22" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.9</v>
+        <v>2.43</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V22" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.82</v>
+        <v>4.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.34</v>
+        <v>1.62</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>2.32</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.95</v>
+        <v>2.55</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.6</v>
+        <v>1.07</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.5</v>
+        <v>1.67</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>1.73</v>
+        <v>4.8</v>
       </c>
       <c r="O25" t="n">
-        <v>4.85</v>
+        <v>2.24</v>
       </c>
       <c r="P25" t="n">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
         <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>6.15</v>
+        <v>6.3</v>
       </c>
       <c r="W25" t="n">
         <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z25" t="n">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH25" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46029.71875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.67</v>
+        <v>4.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>4.8</v>
+        <v>1.73</v>
       </c>
       <c r="O26" t="n">
-        <v>2.24</v>
+        <v>4.85</v>
       </c>
       <c r="P26" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="R26" t="n">
         <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V26" t="n">
-        <v>6.3</v>
+        <v>6.15</v>
       </c>
       <c r="W26" t="n">
         <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46029.71875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1034,7 +1034,7 @@
         <v>2.73</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
         <v>3.32</v>
@@ -1058,7 +1058,7 @@
         <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="AA5" t="n">
         <v>1.55</v>
@@ -1076,10 +1076,10 @@
         <v>1.46</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
         <v>1.41</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>2.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>2.75</v>
       </c>
       <c r="O10" t="n">
-        <v>2.95</v>
+        <v>3.17</v>
       </c>
       <c r="P10" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="Q10" t="n">
         <v>2.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
         <v>4.05</v>
@@ -1638,7 +1638,7 @@
         <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V10" t="n">
         <v>4</v>
@@ -1656,10 +1656,10 @@
         <v>6.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AC10" t="n">
         <v>2.08</v>
@@ -1674,10 +1674,10 @@
         <v>3.16</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46029.5625</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.56</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="O12" t="n">
-        <v>3.02</v>
+        <v>1.86</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.69</v>
+        <v>2.44</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>3.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>2.69</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>3.41</v>
       </c>
       <c r="N13" t="n">
-        <v>10</v>
+        <v>2.47</v>
       </c>
       <c r="O13" t="n">
-        <v>1.86</v>
+        <v>3.02</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.699999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.88</v>
       </c>
-      <c r="T13" t="n">
-        <v>3.05</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="V13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
         <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.58</v>
+        <v>1.69</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.24</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.82</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
-        <v>3.65</v>
+        <v>5.4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.33</v>
+        <v>7.18</v>
       </c>
       <c r="O14" t="n">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.95</v>
+        <v>6.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>2.81</v>
+        <v>3.84</v>
       </c>
       <c r="T14" t="n">
-        <v>3.03</v>
+        <v>2.15</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.41</v>
+        <v>5.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>2.09</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.3</v>
+        <v>2.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
-        <v>2.13</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.84</v>
+        <v>2.65</v>
       </c>
       <c r="P15" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.68</v>
+        <v>3.74</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S15" t="n">
-        <v>3.12</v>
+        <v>3.42</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="U15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V15" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="W15" t="n">
         <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.27</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.75</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>2.08</v>
       </c>
       <c r="O16" t="n">
-        <v>2.39</v>
+        <v>3.84</v>
       </c>
       <c r="P16" t="n">
-        <v>2.07</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>2.68</v>
       </c>
       <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.47</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.36</v>
       </c>
-      <c r="V16" t="n">
-        <v>8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE16" t="n">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.09</v>
+        <v>1.3</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="M17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC17" t="n">
         <v>3.56</v>
       </c>
-      <c r="N17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="AD17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.33</v>
       </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="P18" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.92</v>
+        <v>4.85</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V18" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.77</v>
+        <v>3.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>5.4</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>7.15</v>
+        <v>2.65</v>
       </c>
       <c r="O19" t="n">
-        <v>1.82</v>
+        <v>3.53</v>
       </c>
       <c r="P19" t="n">
-        <v>2.64</v>
+        <v>2.11</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.25</v>
+        <v>2.92</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3.84</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.15</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.05</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2801,16 +2801,16 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.42</v>
+        <v>2.13</v>
       </c>
       <c r="M20" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>3.59</v>
       </c>
       <c r="O20" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="P20" t="n">
         <v>2.05</v>
@@ -2822,46 +2822,46 @@
         <v>1.47</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="U20" t="n">
         <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG20" t="n">
         <v>1.41</v>
@@ -2920,43 +2920,43 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="M21" t="n">
-        <v>2.99</v>
+        <v>2.91</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="P21" t="n">
         <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="R21" t="n">
         <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="U21" t="n">
         <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="W21" t="n">
         <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y21" t="n">
         <v>1.41</v>
@@ -2968,25 +2968,25 @@
         <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD21" t="n">
         <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7.84</v>
+        <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="N22" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="O22" t="n">
-        <v>7.72</v>
+        <v>7.83</v>
       </c>
       <c r="P22" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R22" t="n">
         <v>1.31</v>
@@ -3063,19 +3063,19 @@
         <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="V22" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
         <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
         <v>1.18</v>
@@ -3087,25 +3087,25 @@
         <v>1.62</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>2.95</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3396,40 +3396,40 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M25" t="n">
         <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
         <v>2.24</v>
       </c>
       <c r="P25" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
         <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T25" t="n">
         <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V25" t="n">
         <v>6.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
         <v>1.05</v>
@@ -3459,10 +3459,10 @@
         <v>1.96</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46029.71875</v>
@@ -3515,16 +3515,16 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N26" t="n">
         <v>1.73</v>
       </c>
       <c r="O26" t="n">
-        <v>4.85</v>
+        <v>3.86</v>
       </c>
       <c r="P26" t="n">
         <v>2.27</v>
@@ -3542,13 +3542,13 @@
         <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
         <v>6.15</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
         <v>1.04</v>
@@ -3557,13 +3557,13 @@
         <v>1.21</v>
       </c>
       <c r="Z26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC26" t="n">
         <v>2.68</v>
@@ -3578,7 +3578,7 @@
         <v>2.07</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AH26" t="n">
         <v>1.22</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1031,7 +1031,7 @@
         <v>2.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
@@ -1052,10 +1052,10 @@
         <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
         <v>4.65</v>
@@ -1076,13 +1076,13 @@
         <v>1.46</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AG5" t="n">
         <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46029.47916666666</v>
@@ -1629,7 +1629,7 @@
         <v>2.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="S10" t="n">
         <v>4.05</v>
@@ -1638,7 +1638,7 @@
         <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="V10" t="n">
         <v>4</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.41</v>
+        <v>2.69</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4</v>
+        <v>3.41</v>
       </c>
       <c r="N12" t="n">
-        <v>7.4</v>
+        <v>2.47</v>
       </c>
       <c r="O12" t="n">
-        <v>1.86</v>
+        <v>3.02</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.699999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.4</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.44</v>
+        <v>1.69</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.24</v>
+        <v>1.48</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.69</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>3.41</v>
+        <v>4.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.47</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.02</v>
+        <v>1.94</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T13" t="n">
         <v>3.05</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.88</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.69</v>
+        <v>2.44</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>3.24</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2087,19 +2087,19 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
-        <v>5.4</v>
+        <v>5.15</v>
       </c>
       <c r="N14" t="n">
-        <v>7.18</v>
+        <v>7.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="P14" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
         <v>6.25</v>
@@ -2117,22 +2117,22 @@
         <v>1.73</v>
       </c>
       <c r="V14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z14" t="n">
         <v>5.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB14" t="n">
         <v>2.8</v>
@@ -2144,16 +2144,16 @@
         <v>1.75</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AG14" t="n">
         <v>1.19</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2215,13 +2215,13 @@
         <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="P15" t="n">
         <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="R15" t="n">
         <v>1.31</v>
@@ -2230,25 +2230,25 @@
         <v>3.42</v>
       </c>
       <c r="T15" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="U15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="W15" t="n">
         <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
         <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA15" t="n">
         <v>1.7</v>
@@ -2257,7 +2257,7 @@
         <v>2.15</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AD15" t="n">
         <v>1.38</v>
@@ -2272,7 +2272,7 @@
         <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.45</v>
+        <v>1.88</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.08</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.84</v>
+        <v>2.47</v>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.68</v>
+        <v>4.86</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>3.31</v>
+        <v>2.81</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="U16" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>2.02</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.67</v>
+        <v>3.45</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>5.4</v>
+        <v>2.08</v>
       </c>
       <c r="O17" t="n">
-        <v>2.38</v>
+        <v>3.88</v>
       </c>
       <c r="P17" t="n">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>2.67</v>
+        <v>3.18</v>
       </c>
       <c r="T17" t="n">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.04</v>
+        <v>3.74</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.56</v>
+        <v>2.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="AG17" t="n">
         <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.09</v>
+        <v>1.26</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="P18" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>2.81</v>
+        <v>2.67</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.34</v>
+        <v>3.56</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2691,19 +2691,19 @@
         <v>2.65</v>
       </c>
       <c r="O19" t="n">
-        <v>3.53</v>
+        <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T19" t="n">
         <v>2.75</v>
@@ -2733,22 +2733,22 @@
         <v>1.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD19" t="n">
         <v>1.29</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AF19" t="n">
         <v>2.15</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,43 +2801,43 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="M20" t="n">
-        <v>3.11</v>
+        <v>2.91</v>
       </c>
       <c r="N20" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y20" t="n">
         <v>1.38</v>
@@ -2846,28 +2846,28 @@
         <v>2.77</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.86</v>
+        <v>4.33</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG20" t="n">
         <v>1.41</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="M21" t="n">
-        <v>2.91</v>
+        <v>3.11</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="O21" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>9.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.41</v>
       </c>
-      <c r="Z21" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3048,7 +3048,7 @@
         <v>1.38</v>
       </c>
       <c r="O22" t="n">
-        <v>7.83</v>
+        <v>6.6</v>
       </c>
       <c r="P22" t="n">
         <v>2.65</v>
@@ -3060,28 +3060,28 @@
         <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="W22" t="n">
         <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA22" t="n">
         <v>1.62</v>
@@ -3096,16 +3096,16 @@
         <v>1.47</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.95</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O25" t="n">
         <v>2.24</v>
@@ -3411,19 +3411,19 @@
         <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="S25" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="T25" t="n">
         <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V25" t="n">
         <v>6.3</v>
@@ -3453,13 +3453,13 @@
         <v>1.38</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AF25" t="n">
         <v>1.96</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AH25" t="n">
         <v>2.24</v>
@@ -3524,7 +3524,7 @@
         <v>1.73</v>
       </c>
       <c r="O26" t="n">
-        <v>3.86</v>
+        <v>4.95</v>
       </c>
       <c r="P26" t="n">
         <v>2.27</v>
@@ -3539,13 +3539,13 @@
         <v>3.18</v>
       </c>
       <c r="T26" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="U26" t="n">
         <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>6.15</v>
+        <v>6.1</v>
       </c>
       <c r="W26" t="n">
         <v>1.09</v>
@@ -3557,7 +3557,7 @@
         <v>1.21</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AA26" t="n">
         <v>1.7</v>
@@ -3566,22 +3566,22 @@
         <v>2.15</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE26" t="n">
         <v>1.69</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46029.71875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI30"/>
+  <dimension ref="A1:AI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.36</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>5.15</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>7.6</v>
+        <v>2.65</v>
       </c>
       <c r="O14" t="n">
-        <v>1.79</v>
+        <v>3.7</v>
       </c>
       <c r="P14" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.25</v>
+        <v>2.77</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>3.84</v>
+        <v>2.98</v>
       </c>
       <c r="T14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.15</v>
       </c>
-      <c r="U14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.19</v>
+        <v>1.63</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.05</v>
+        <v>1.39</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="P15" t="n">
         <v>2.13</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q15" t="n">
-        <v>3.92</v>
+        <v>4.86</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>3.42</v>
+        <v>2.81</v>
       </c>
       <c r="T15" t="n">
-        <v>2.58</v>
+        <v>3.04</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.76</v>
+        <v>3.34</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.88</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>2.08</v>
       </c>
       <c r="O16" t="n">
-        <v>2.47</v>
+        <v>3.88</v>
       </c>
       <c r="P16" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.86</v>
+        <v>2.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>2.81</v>
+        <v>3.18</v>
       </c>
       <c r="T16" t="n">
-        <v>3.04</v>
+        <v>2.66</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="V16" t="n">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.14</v>
+        <v>3.74</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.02</v>
+        <v>1.26</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.45</v>
+        <v>2.13</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N17" t="n">
-        <v>2.08</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3.88</v>
+        <v>2.45</v>
       </c>
       <c r="P17" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.62</v>
+        <v>3.92</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="T17" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="U17" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="W17" t="n">
         <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
         <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>5.15</v>
       </c>
       <c r="N18" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="O18" t="n">
-        <v>2.38</v>
+        <v>1.79</v>
       </c>
       <c r="P18" t="n">
-        <v>2.03</v>
+        <v>2.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>2.67</v>
+        <v>3.84</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.1</v>
+        <v>5.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.77</v>
+        <v>2.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.56</v>
+        <v>2.09</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.86</v>
+        <v>2.17</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.09</v>
+        <v>3.05</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.65</v>
+        <v>5.4</v>
       </c>
       <c r="O19" t="n">
-        <v>3.7</v>
+        <v>2.38</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.77</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
-        <v>2.98</v>
+        <v>2.67</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.2</v>
+        <v>3.56</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.39</v>
+        <v>2.09</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="M20" t="n">
-        <v>2.91</v>
+        <v>3.11</v>
       </c>
       <c r="N20" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="O20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T20" t="n">
         <v>3.05</v>
       </c>
-      <c r="P20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.15</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
         <v>1.41</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.13</v>
+        <v>7.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.11</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
-        <v>3.59</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.98</v>
+        <v>1.86</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.47</v>
       </c>
-      <c r="T21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V21" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4.25</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AE21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1.87</v>
       </c>
-      <c r="AF21" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.59</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,61 +3039,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7.3</v>
+        <v>2.26</v>
       </c>
       <c r="M22" t="n">
-        <v>4.8</v>
+        <v>2.91</v>
       </c>
       <c r="N22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V22" t="n">
+        <v>9</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.38</v>
       </c>
-      <c r="O22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z22" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC22" t="n">
         <v>4.33</v>
       </c>
-      <c r="AA22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.47</v>
-      </c>
       <c r="AD22" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
         <v>1.85</v>
@@ -3102,10 +3102,10 @@
         <v>1.87</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3585,482 +3585,6 @@
       </c>
       <c r="AI26" s="3" t="n">
         <v>46029.71875</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46029</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>USM Alger</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>MC Oran</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="3" t="n">
-        <v>46029.875</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>46029</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>El Bayadh</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ES Mostaganem</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="3" t="n">
-        <v>46029.875</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46029</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>ES Sétif</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Paradou AC</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="3" t="n">
-        <v>46029.875</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46029</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Ben Aknoun</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Oued Akbou</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" s="3" t="n">
-        <v>46029.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.69</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
-        <v>3.41</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.47</v>
+        <v>7.4</v>
       </c>
       <c r="O12" t="n">
-        <v>3.02</v>
+        <v>1.94</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.44</v>
+        <v>3.39</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.35</v>
+        <v>3.67</v>
       </c>
       <c r="AD12" t="n">
         <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.69</v>
+        <v>2.44</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.48</v>
+        <v>3.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>2.69</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4</v>
+        <v>3.41</v>
       </c>
       <c r="N13" t="n">
-        <v>7.4</v>
+        <v>2.47</v>
       </c>
       <c r="O13" t="n">
-        <v>1.94</v>
+        <v>3.02</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.699999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.4</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.39</v>
+        <v>3.44</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.67</v>
+        <v>3.35</v>
       </c>
       <c r="AD13" t="n">
         <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.44</v>
+        <v>1.69</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.24</v>
+        <v>1.48</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.65</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.7</v>
+        <v>2.47</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.77</v>
+        <v>4.86</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.78</v>
+        <v>3.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.63</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.39</v>
+        <v>2.02</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="P15" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.81</v>
+        <v>2.67</v>
       </c>
       <c r="T15" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.34</v>
+        <v>3.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.45</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>5.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.08</v>
+        <v>7.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.88</v>
+        <v>1.79</v>
       </c>
       <c r="P16" t="n">
-        <v>2.23</v>
+        <v>2.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.62</v>
+        <v>6.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>3.18</v>
+        <v>3.84</v>
       </c>
       <c r="T16" t="n">
-        <v>2.66</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="V16" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.74</v>
+        <v>5.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.9</v>
+        <v>2.09</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.26</v>
+        <v>3.05</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>5.15</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>7.6</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
-        <v>1.79</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.25</v>
+        <v>2.77</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>3.84</v>
+        <v>2.98</v>
       </c>
       <c r="T18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF18" t="n">
         <v>2.15</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.19</v>
+        <v>1.63</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.05</v>
+        <v>1.39</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>3.45</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>5.4</v>
+        <v>2.08</v>
       </c>
       <c r="O19" t="n">
-        <v>2.38</v>
+        <v>3.88</v>
       </c>
       <c r="P19" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="R19" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>2.67</v>
+        <v>3.18</v>
       </c>
       <c r="T19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.9</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V19" t="n">
-        <v>8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.56</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
         <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.09</v>
+        <v>1.26</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.13</v>
+        <v>7.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.11</v>
+        <v>4.8</v>
       </c>
       <c r="N20" t="n">
-        <v>3.59</v>
+        <v>1.38</v>
       </c>
       <c r="O20" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.98</v>
+        <v>1.86</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.47</v>
       </c>
-      <c r="T20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.25</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AE20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.87</v>
       </c>
-      <c r="AF20" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.59</v>
+        <v>1.09</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7.3</v>
+        <v>2.13</v>
       </c>
       <c r="M21" t="n">
-        <v>4.8</v>
+        <v>3.11</v>
       </c>
       <c r="N21" t="n">
-        <v>1.38</v>
+        <v>3.59</v>
       </c>
       <c r="O21" t="n">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="P21" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.86</v>
+        <v>3.98</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>3.6</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="U21" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>5.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.47</v>
+        <v>4.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>1.59</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46029.41666666666</v>
@@ -1025,7 +1025,7 @@
         <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>3.53</v>
+        <v>3.42</v>
       </c>
       <c r="P5" t="n">
         <v>2.21</v>
@@ -1052,7 +1052,7 @@
         <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
         <v>1.17</v>
@@ -1082,7 +1082,7 @@
         <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46029.47916666666</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.25</v>
+        <v>9.5</v>
       </c>
       <c r="M7" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="N7" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46029.53125</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1632,13 +1632,13 @@
         <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V10" t="n">
         <v>4</v>
@@ -1650,10 +1650,10 @@
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="AA10" t="n">
         <v>1.35</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.41</v>
+        <v>2.69</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4</v>
+        <v>3.41</v>
       </c>
       <c r="N12" t="n">
-        <v>7.4</v>
+        <v>2.47</v>
       </c>
       <c r="O12" t="n">
-        <v>1.94</v>
+        <v>3.02</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.699999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="U12" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="W12" t="n">
         <v>1.04</v>
@@ -1888,34 +1888,34 @@
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.39</v>
+        <v>3.44</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.67</v>
+        <v>3.22</v>
       </c>
       <c r="AD12" t="n">
         <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.44</v>
+        <v>1.69</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.24</v>
+        <v>1.48</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.69</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>3.41</v>
+        <v>4.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.47</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.02</v>
+        <v>1.94</v>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>6.18</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
         <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.44</v>
+        <v>3.39</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AD13" t="n">
         <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.69</v>
+        <v>2.41</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.04</v>
+        <v>1.51</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.48</v>
+        <v>3.24</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.88</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="N14" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V14" t="n">
         <v>4.4</v>
       </c>
-      <c r="O14" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T14" t="n">
+      <c r="W14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH14" t="n">
         <v>3.04</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.02</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH15" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.36</v>
       </c>
-      <c r="M16" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="N16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="V16" t="n">
+        <v>8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.24</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="AE16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH16" t="n">
         <v>2.09</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>3.05</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.13</v>
+        <v>3.45</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="O17" t="n">
-        <v>2.45</v>
+        <v>3.88</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.92</v>
+        <v>2.62</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.42</v>
+        <v>3.12</v>
       </c>
       <c r="T17" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V17" t="n">
-        <v>6.3</v>
+        <v>5.95</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2572,25 +2572,25 @@
         <v>2.65</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
         <v>2.98</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="U18" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="V18" t="n">
         <v>7</v>
@@ -2599,7 +2599,7 @@
         <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
         <v>1.26</v>
@@ -2626,10 +2626,10 @@
         <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.45</v>
+        <v>2.13</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>2.08</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>3.88</v>
+        <v>2.66</v>
       </c>
       <c r="P19" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.62</v>
+        <v>3.72</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="U19" t="n">
         <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AG19" t="n">
         <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.3</v>
+        <v>2.13</v>
       </c>
       <c r="M20" t="n">
-        <v>4.8</v>
+        <v>3.11</v>
       </c>
       <c r="N20" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.38</v>
       </c>
-      <c r="O20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z20" t="n">
-        <v>4.33</v>
+        <v>2.99</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.47</v>
+        <v>4.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.09</v>
+        <v>1.59</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="M21" t="n">
-        <v>3.11</v>
+        <v>2.91</v>
       </c>
       <c r="N21" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="S21" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>3.05</v>
+        <v>3.41</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1.87</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
         <v>1.41</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,61 +3039,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.26</v>
+        <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>2.91</v>
+        <v>4.8</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>1.38</v>
       </c>
       <c r="O22" t="n">
-        <v>3.05</v>
+        <v>5.32</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.1</v>
+        <v>1.84</v>
       </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>2.39</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="V22" t="n">
-        <v>9</v>
+        <v>5.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.77</v>
+        <v>4.33</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB22" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AC22" t="n">
-        <v>4.33</v>
+        <v>2.47</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="AE22" t="n">
         <v>1.85</v>
@@ -3102,10 +3102,10 @@
         <v>1.87</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.63</v>
+        <v>1.09</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3396,16 +3396,16 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="P25" t="n">
         <v>2.4</v>
@@ -3414,22 +3414,22 @@
         <v>5.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="T25" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
         <v>1.46</v>
       </c>
       <c r="V25" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
         <v>1.05</v>
@@ -3444,10 +3444,10 @@
         <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="AD25" t="n">
         <v>1.38</v>
@@ -3524,13 +3524,13 @@
         <v>1.73</v>
       </c>
       <c r="O26" t="n">
-        <v>4.95</v>
+        <v>3.86</v>
       </c>
       <c r="P26" t="n">
         <v>2.27</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R26" t="n">
         <v>1.35</v>
@@ -3545,7 +3545,7 @@
         <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="W26" t="n">
         <v>1.09</v>
@@ -3557,7 +3557,7 @@
         <v>1.21</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="AA26" t="n">
         <v>1.7</v>
@@ -3578,7 +3578,7 @@
         <v>2.04</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
         <v>1.21</v>

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="M2" t="n">
-        <v>3.59</v>
+        <v>3.87</v>
       </c>
       <c r="N2" t="n">
-        <v>5.2</v>
+        <v>5.72</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46029.41319444445</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.65</v>
+        <v>3.89</v>
       </c>
       <c r="N3" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="O3" t="n">
-        <v>5.27</v>
+        <v>5.36</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V3" t="n">
-        <v>6.55</v>
+        <v>6.15</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46029.41666666666</v>
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.55</v>
+        <v>2.84</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N5" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="O5" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
         <v>2.21</v>
@@ -1034,7 +1034,7 @@
         <v>2.71</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
         <v>3.32</v>
@@ -1064,25 +1064,25 @@
         <v>1.55</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AE5" t="n">
         <v>1.46</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AG5" t="n">
         <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46029.47916666666</v>
@@ -1611,37 +1611,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>2.61</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>4.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="O10" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
         <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
         <v>1.77</v>
       </c>
       <c r="V10" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="W10" t="n">
         <v>1.17</v>
@@ -1656,25 +1656,25 @@
         <v>6.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="n">
         <v>1.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.16</v>
+        <v>3.03</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
         <v>1.38</v>
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.41</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="O12" t="n">
-        <v>3.02</v>
+        <v>3.44</v>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
@@ -1873,13 +1873,13 @@
         <v>2.96</v>
       </c>
       <c r="T12" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="W12" t="n">
         <v>1.04</v>
@@ -1888,31 +1888,31 @@
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="AD12" t="n">
         <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AH12" t="n">
         <v>1.48</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="N13" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>2.41</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.18</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
@@ -1992,49 +1992,49 @@
         <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
         <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="AD13" t="n">
         <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AF13" t="n">
         <v>1.51</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="M14" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>7.3</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.82</v>
+        <v>2.38</v>
       </c>
       <c r="P14" t="n">
-        <v>2.64</v>
+        <v>2.03</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.3</v>
+        <v>4.9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8</v>
+        <v>2.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>3.12</v>
       </c>
       <c r="U14" t="n">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.55</v>
+        <v>3.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.04</v>
+        <v>2.09</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>2.65</v>
       </c>
       <c r="O15" t="n">
-        <v>2.58</v>
+        <v>3.66</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.86</v>
+        <v>2.92</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>2.81</v>
+        <v>2.98</v>
       </c>
       <c r="T15" t="n">
-        <v>3.04</v>
+        <v>2.86</v>
       </c>
       <c r="U15" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="V15" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.06</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.14</v>
+        <v>3.78</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.67</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>5.4</v>
+        <v>2.08</v>
       </c>
       <c r="O16" t="n">
-        <v>2.38</v>
+        <v>3.88</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.9</v>
+        <v>2.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>2.67</v>
+        <v>3.12</v>
       </c>
       <c r="T16" t="n">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="U16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.36</v>
       </c>
-      <c r="V16" t="n">
-        <v>8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.09</v>
+        <v>1.34</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.45</v>
+        <v>1.39</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="N17" t="n">
-        <v>2.08</v>
+        <v>7.3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.88</v>
+        <v>1.82</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.62</v>
+        <v>6.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.66</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="V17" t="n">
-        <v>5.95</v>
+        <v>4.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.74</v>
+        <v>5.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.75</v>
+        <v>1.19</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.34</v>
+        <v>3.04</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>3.66</v>
+        <v>2.58</v>
       </c>
       <c r="P18" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.92</v>
+        <v>4.86</v>
       </c>
       <c r="R18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.39</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.45</v>
-      </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.78</v>
+        <v>3.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="P20" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="T20" t="n">
-        <v>3.28</v>
+        <v>3.41</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG20" t="n">
         <v>1.41</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="M21" t="n">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="O21" t="n">
         <v>3.05</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
         <v>1.51</v>
       </c>
       <c r="S21" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="T21" t="n">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
         <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AA21" t="n">
         <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3039,31 +3039,31 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="M22" t="n">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="N22" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O22" t="n">
-        <v>5.32</v>
+        <v>6.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
         <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
         <v>1.53</v>
@@ -3075,7 +3075,7 @@
         <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
         <v>1.17</v>
@@ -3087,22 +3087,22 @@
         <v>1.62</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
         <v>1.09</v>

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46029.48263888889</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>9.5</v>
+        <v>6.02</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="O7" t="n">
-        <v>6.06</v>
+        <v>5.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q7" t="n">
         <v>2.04</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V7" t="n">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.15</v>
+        <v>2.39</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46029.53125</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46029.53819444445</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>1.19</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>4.75</v>
       </c>
       <c r="N12" t="n">
-        <v>2.63</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>3.44</v>
+        <v>1.92</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AB12" t="n">
         <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.45</v>
+        <v>3.67</v>
       </c>
       <c r="AD12" t="n">
         <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.51</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.46</v>
+        <v>1.07</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.48</v>
+        <v>3</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.19</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="n">
-        <v>4.75</v>
+        <v>3.05</v>
       </c>
       <c r="N13" t="n">
-        <v>9.800000000000001</v>
+        <v>2.63</v>
       </c>
       <c r="O13" t="n">
-        <v>1.92</v>
+        <v>3.44</v>
       </c>
       <c r="P13" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
       </c>
       <c r="S13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.88</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
         <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.67</v>
+        <v>3.45</v>
       </c>
       <c r="AD13" t="n">
         <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.51</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.07</v>
+        <v>1.46</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>1.48</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.67</v>
+        <v>3.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>2.08</v>
       </c>
       <c r="O14" t="n">
-        <v>2.38</v>
+        <v>3.88</v>
       </c>
       <c r="P14" t="n">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.9</v>
+        <v>2.62</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.67</v>
+        <v>3.12</v>
       </c>
       <c r="T14" t="n">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="U14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.36</v>
       </c>
-      <c r="V14" t="n">
-        <v>8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.09</v>
+        <v>1.34</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.66</v>
+        <v>2.66</v>
       </c>
       <c r="P15" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.92</v>
+        <v>3.72</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="U15" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="W15" t="n">
         <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M16" t="n">
         <v>3.45</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.55</v>
-      </c>
       <c r="N16" t="n">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="O16" t="n">
-        <v>3.88</v>
+        <v>3.66</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>3.12</v>
+        <v>2.98</v>
       </c>
       <c r="T16" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="U16" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V16" t="n">
-        <v>5.95</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="M17" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>7.3</v>
+        <v>5.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.82</v>
+        <v>2.38</v>
       </c>
       <c r="P17" t="n">
-        <v>2.64</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.3</v>
+        <v>4.9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>2.67</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>3.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.55</v>
+        <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.04</v>
+        <v>2.09</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.13</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.66</v>
+        <v>1.82</v>
       </c>
       <c r="P19" t="n">
-        <v>2.21</v>
+        <v>2.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.72</v>
+        <v>6.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.58</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.1</v>
+        <v>5.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.73</v>
+        <v>3.04</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.05</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.94</v>
-      </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="S20" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="T20" t="n">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="U20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AF20" t="n">
         <v>1.86</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.36</v>
+        <v>7.5</v>
       </c>
       <c r="M21" t="n">
-        <v>2.98</v>
+        <v>4.65</v>
       </c>
       <c r="N21" t="n">
-        <v>2.85</v>
+        <v>1.4</v>
       </c>
       <c r="O21" t="n">
-        <v>3.05</v>
+        <v>6.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>1.85</v>
       </c>
       <c r="R21" t="n">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.34</v>
+        <v>2.23</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.61</v>
+        <v>2.31</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.05</v>
+        <v>2.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AF21" t="n">
         <v>1.86</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="M22" t="n">
-        <v>4.65</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>6.5</v>
+        <v>3.04</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.85</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="T22" t="n">
-        <v>2.23</v>
+        <v>3.41</v>
       </c>
       <c r="U22" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>5.25</v>
+        <v>9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AF22" t="n">
         <v>1.86</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.09</v>
+        <v>1.62</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.54</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
         <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>1.73</v>
       </c>
       <c r="O25" t="n">
-        <v>2.23</v>
+        <v>3.86</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.4</v>
+        <v>2.25</v>
       </c>
       <c r="R25" t="n">
         <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U25" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>5.8</v>
+        <v>6.15</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.64</v>
+        <v>4.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC25" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AG25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.21</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.24</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46029.71875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>1.54</v>
       </c>
       <c r="M26" t="n">
         <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>1.73</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>3.86</v>
+        <v>2.23</v>
       </c>
       <c r="P26" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.25</v>
+        <v>5.4</v>
       </c>
       <c r="R26" t="n">
         <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V26" t="n">
-        <v>6.15</v>
+        <v>5.8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.21</v>
+        <v>2.24</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46029.71875</v>

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.19</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4.75</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>9.800000000000001</v>
+        <v>2.63</v>
       </c>
       <c r="O12" t="n">
-        <v>1.92</v>
+        <v>3.44</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.88</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
         <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.67</v>
+        <v>3.45</v>
       </c>
       <c r="AD12" t="n">
         <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.51</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.07</v>
+        <v>1.46</v>
       </c>
       <c r="AH12" t="n">
-        <v>3</v>
+        <v>1.48</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.8</v>
+        <v>1.19</v>
       </c>
       <c r="M13" t="n">
-        <v>3.05</v>
+        <v>4.75</v>
       </c>
       <c r="N13" t="n">
-        <v>2.63</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>3.44</v>
+        <v>1.92</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AB13" t="n">
         <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.45</v>
+        <v>3.67</v>
       </c>
       <c r="AD13" t="n">
         <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>1.51</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.46</v>
+        <v>1.07</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.48</v>
+        <v>3</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.45</v>
+        <v>1.88</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.08</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.88</v>
+        <v>2.58</v>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.62</v>
+        <v>4.86</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>3.12</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
-        <v>2.66</v>
+        <v>3.04</v>
       </c>
       <c r="U14" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>5.95</v>
+        <v>7.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.74</v>
+        <v>3.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH14" t="n">
         <v>2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.34</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.13</v>
+        <v>3.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="O15" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.66</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.58</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="V15" t="n">
-        <v>5.8</v>
+        <v>5.95</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N16" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
-        <v>3.66</v>
+        <v>2.66</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.92</v>
+        <v>3.72</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="U16" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="W16" t="n">
         <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>5.4</v>
+        <v>2.65</v>
       </c>
       <c r="O17" t="n">
-        <v>2.38</v>
+        <v>3.66</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.9</v>
+        <v>2.92</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>2.67</v>
+        <v>2.98</v>
       </c>
       <c r="T17" t="n">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="U17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.36</v>
       </c>
-      <c r="V17" t="n">
-        <v>8</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH17" t="n">
-        <v>2.09</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.88</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="N18" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V18" t="n">
         <v>4.4</v>
       </c>
-      <c r="O18" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="W18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH18" t="n">
         <v>3.04</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>7.3</v>
+        <v>5.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.82</v>
+        <v>2.38</v>
       </c>
       <c r="P19" t="n">
-        <v>2.64</v>
+        <v>2.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.3</v>
+        <v>4.9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
-        <v>3.8</v>
+        <v>2.67</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>3.12</v>
       </c>
       <c r="U19" t="n">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.55</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.04</v>
+        <v>2.09</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.36</v>
+        <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>2.98</v>
+        <v>4.65</v>
       </c>
       <c r="N20" t="n">
-        <v>2.85</v>
+        <v>1.4</v>
       </c>
       <c r="O20" t="n">
-        <v>3.05</v>
+        <v>6.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>1.85</v>
       </c>
       <c r="R20" t="n">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>3.34</v>
+        <v>2.23</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.61</v>
+        <v>2.31</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.05</v>
+        <v>2.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AF20" t="n">
         <v>1.86</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7.5</v>
+        <v>2.36</v>
       </c>
       <c r="M21" t="n">
-        <v>4.65</v>
+        <v>2.98</v>
       </c>
       <c r="N21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.4</v>
       </c>
-      <c r="O21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z21" t="n">
-        <v>4.33</v>
+        <v>2.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.31</v>
+        <v>1.61</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.55</v>
+        <v>4.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AF21" t="n">
         <v>1.86</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -659,34 +659,34 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="M2" t="n">
-        <v>3.87</v>
+        <v>3.59</v>
       </c>
       <c r="N2" t="n">
-        <v>5.72</v>
+        <v>5.2</v>
       </c>
       <c r="O2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.35</v>
+        <v>6.49</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="T2" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="U2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
         <v>6</v>
@@ -704,16 +704,16 @@
         <v>3.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE2" t="n">
         <v>1.95</v>
@@ -725,7 +725,7 @@
         <v>1.19</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46029.41319444445</v>
@@ -778,37 +778,37 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.89</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="O3" t="n">
-        <v>5.36</v>
+        <v>5.31</v>
       </c>
       <c r="P3" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
         <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="U3" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="V3" t="n">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="W3" t="n">
         <v>1.06</v>
@@ -817,31 +817,31 @@
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AF3" t="n">
         <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH3" t="n">
         <v>1.12</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1135,37 +1135,37 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O6" t="n">
-        <v>6.2</v>
+        <v>6.15</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="U6" t="n">
         <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.06</v>
@@ -1174,22 +1174,22 @@
         <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
         <v>2.06</v>
@@ -1198,10 +1198,10 @@
         <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46029.48263888889</v>
@@ -1254,28 +1254,28 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.02</v>
+        <v>9.5</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="N7" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
         <v>5.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="T7" t="n">
         <v>2.44</v>
@@ -1290,37 +1290,37 @@
         <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
         <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46029.53125</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="M8" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="P8" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="U8" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V8" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.47</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.54</v>
       </c>
       <c r="AG8" t="n">
         <v>1.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46029.53819444445</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.63</v>
+        <v>8.76</v>
       </c>
       <c r="O12" t="n">
-        <v>3.44</v>
+        <v>1.9</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U12" t="n">
         <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="AA12" t="n">
         <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.45</v>
+        <v>3.67</v>
       </c>
       <c r="AD12" t="n">
         <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.51</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.46</v>
+        <v>1.11</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.48</v>
+        <v>3</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.19</v>
+        <v>2.75</v>
       </c>
       <c r="M13" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>9.800000000000001</v>
+        <v>2.52</v>
       </c>
       <c r="O13" t="n">
-        <v>1.92</v>
+        <v>3.52</v>
       </c>
       <c r="P13" t="n">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>3.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
         <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD13" t="n">
         <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.51</v>
+        <v>2.04</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.07</v>
+        <v>1.49</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>1.42</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.88</v>
+        <v>1.28</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>4.85</v>
       </c>
       <c r="N14" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V14" t="n">
         <v>4.4</v>
       </c>
-      <c r="O14" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.3</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.14</v>
+        <v>5.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>2.95</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.34</v>
+        <v>2.09</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.31</v>
+        <v>1.79</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
         <v>1.33</v>
@@ -2230,46 +2230,46 @@
         <v>3.12</v>
       </c>
       <c r="T15" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="V15" t="n">
-        <v>5.95</v>
+        <v>5.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
         <v>1.34</v>
@@ -2325,31 +2325,31 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="O16" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="R16" t="n">
         <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="T16" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
         <v>1.48</v>
@@ -2358,40 +2358,40 @@
         <v>5.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
         <v>1.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>4.58</v>
       </c>
       <c r="O17" t="n">
-        <v>3.66</v>
+        <v>2.45</v>
       </c>
       <c r="P17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.92</v>
+        <v>4.14</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="U17" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.78</v>
+        <v>3.14</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>2.03</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.39</v>
-      </c>
-      <c r="M18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N18" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>3.04</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2682,31 +2682,31 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="N19" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="P19" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
         <v>2.67</v>
       </c>
       <c r="T19" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="U19" t="n">
         <v>1.36</v>
@@ -2721,16 +2721,16 @@
         <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
         <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC19" t="n">
         <v>3.56</v>
@@ -2739,16 +2739,16 @@
         <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
         <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
         <v>1.4</v>
@@ -2813,10 +2813,10 @@
         <v>6.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="R20" t="n">
         <v>1.29</v>
@@ -2840,31 +2840,31 @@
         <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
         <v>1.09</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
         <v>3.05</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="T21" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="M22" t="n">
         <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="O22" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
         <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3396,40 +3396,40 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>5.07</v>
       </c>
       <c r="M25" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O25" t="n">
-        <v>3.86</v>
+        <v>5.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
         <v>3.18</v>
       </c>
       <c r="T25" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="U25" t="n">
         <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>6.15</v>
+        <v>5.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
         <v>1.04</v>
@@ -3438,31 +3438,31 @@
         <v>1.21</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="AD25" t="n">
         <v>1.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AF25" t="n">
         <v>2.04</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46029.71875</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="M26" t="n">
         <v>3.9</v>
@@ -3524,64 +3524,64 @@
         <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="U26" t="n">
         <v>1.46</v>
       </c>
       <c r="V26" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC26" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46029.71875</v>

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>3.51</v>
       </c>
       <c r="P5" t="n">
         <v>2.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
@@ -1055,7 +1055,7 @@
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z5" t="n">
         <v>4.65</v>
@@ -1064,13 +1064,13 @@
         <v>1.55</v>
       </c>
       <c r="AB5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.29</v>
       </c>
-      <c r="AC5" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="n">
         <v>1.46</v>
@@ -1082,7 +1082,7 @@
         <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46029.47916666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,25 +1611,25 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.61</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>4.12</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="S10" t="n">
         <v>4.1</v>
@@ -1644,34 +1644,34 @@
         <v>3.98</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z10" t="n">
         <v>6.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
         <v>1.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="AG10" t="n">
         <v>1.22</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>2.69</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>3.41</v>
       </c>
       <c r="N12" t="n">
-        <v>8.76</v>
+        <v>2.47</v>
       </c>
       <c r="O12" t="n">
-        <v>1.9</v>
+        <v>3.52</v>
       </c>
       <c r="P12" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.85</v>
+        <v>3.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
         <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.39</v>
+        <v>3.44</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
         <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.51</v>
+        <v>2.04</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.11</v>
+        <v>1.49</v>
       </c>
       <c r="AH12" t="n">
-        <v>3</v>
+        <v>1.42</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.52</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.52</v>
+        <v>1.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
         <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.44</v>
+        <v>3.39</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="AD13" t="n">
         <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.04</v>
+        <v>1.51</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.42</v>
+        <v>3</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.28</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>4.85</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>6.92</v>
+        <v>2.65</v>
       </c>
       <c r="O14" t="n">
-        <v>1.8</v>
+        <v>3.74</v>
       </c>
       <c r="P14" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9</v>
+        <v>3.06</v>
       </c>
       <c r="T14" t="n">
-        <v>1.98</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>4.4</v>
+        <v>6.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.09</v>
+        <v>3.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.79</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.9</v>
+        <v>1.39</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.25</v>
+        <v>1.88</v>
       </c>
       <c r="M15" t="n">
         <v>3.4</v>
       </c>
       <c r="N15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P15" t="n">
         <v>2.1</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.36</v>
-      </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>4.95</v>
       </c>
       <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.33</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.23</v>
-      </c>
       <c r="Z15" t="n">
-        <v>3.68</v>
+        <v>3.14</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.01</v>
+        <v>3.34</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.34</v>
+        <v>2.04</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.15</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>3.24</v>
+        <v>2.08</v>
       </c>
       <c r="O16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2.5</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.9</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="T16" t="n">
         <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="V16" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="N17" t="n">
-        <v>4.58</v>
+        <v>6.97</v>
       </c>
       <c r="O17" t="n">
-        <v>2.45</v>
+        <v>1.84</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.14</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.93</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.4</v>
       </c>
-      <c r="V17" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.34</v>
+        <v>2.09</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.27</v>
+        <v>1.86</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.86</v>
+        <v>2.28</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.03</v>
+        <v>2.96</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>5.4</v>
       </c>
       <c r="O18" t="n">
-        <v>3.74</v>
+        <v>2.39</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
         <v>1.38</v>
       </c>
       <c r="S18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z18" t="n">
         <v>3.1</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M19" t="n">
-        <v>3.54</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>3.94</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>2.67</v>
+        <v>3.24</v>
       </c>
       <c r="T19" t="n">
-        <v>3.17</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.05</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE19" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="AG19" t="n">
         <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="N20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O20" t="n">
         <v>6.5</v>
@@ -2846,10 +2846,10 @@
         <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
         <v>2.47</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
         <v>3.05</v>
@@ -2965,10 +2965,10 @@
         <v>2.73</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AC21" t="n">
         <v>4.33</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.37</v>
+        <v>2.13</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="N22" t="n">
-        <v>3.14</v>
+        <v>3.59</v>
       </c>
       <c r="O22" t="n">
         <v>3.1</v>
@@ -3084,10 +3084,10 @@
         <v>2.66</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
         <v>4.1</v>
@@ -3396,16 +3396,16 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.07</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="O25" t="n">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="P25" t="n">
         <v>2.3</v>
@@ -3414,37 +3414,37 @@
         <v>2.15</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
         <v>3.18</v>
       </c>
       <c r="T25" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="U25" t="n">
         <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>5.5</v>
+        <v>6.15</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
         <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z25" t="n">
         <v>3.98</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC25" t="n">
         <v>2.68</v>
@@ -3536,16 +3536,16 @@
         <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="T26" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="U26" t="n">
         <v>1.46</v>
       </c>
       <c r="V26" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="W26" t="n">
         <v>1.09</v>
@@ -3566,22 +3566,22 @@
         <v>2.06</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.03</v>
+        <v>2.84</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AF26" t="n">
         <v>2.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46029.71875</v>

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -668,13 +668,13 @@
         <v>5.2</v>
       </c>
       <c r="O2" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="P2" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.49</v>
+        <v>6.56</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
@@ -719,13 +719,13 @@
         <v>1.95</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46029.41319444445</v>
@@ -787,19 +787,19 @@
         <v>1.65</v>
       </c>
       <c r="O3" t="n">
-        <v>5.31</v>
+        <v>5.47</v>
       </c>
       <c r="P3" t="n">
         <v>2.17</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="R3" t="n">
         <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="T3" t="n">
         <v>2.59</v>
@@ -832,19 +832,19 @@
         <v>2.83</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AF3" t="n">
         <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.15</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46029.41666666666</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.9</v>
+        <v>3.86</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N4" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1144,37 +1144,37 @@
         <v>1.68</v>
       </c>
       <c r="O6" t="n">
-        <v>6.15</v>
+        <v>5.64</v>
       </c>
       <c r="P6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="T6" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
         <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
         <v>2.74</v>
@@ -1186,16 +1186,16 @@
         <v>1.64</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.88</v>
+        <v>3.96</v>
       </c>
       <c r="AD6" t="n">
         <v>1.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
         <v>1.24</v>
@@ -1263,13 +1263,13 @@
         <v>1.3</v>
       </c>
       <c r="O7" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R7" t="n">
         <v>1.32</v>
@@ -1290,13 +1290,13 @@
         <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
         <v>1.7</v>
@@ -1305,22 +1305,22 @@
         <v>2.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AD7" t="n">
         <v>1.41</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.5</v>
+        <v>1.13</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46029.53125</v>
@@ -1403,13 +1403,13 @@
         <v>1.45</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
         <v>1.17</v>
@@ -1424,22 +1424,22 @@
         <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG8" t="n">
         <v>1.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46029.53819444445</v>
@@ -1858,37 +1858,37 @@
         <v>2.47</v>
       </c>
       <c r="O12" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="P12" t="n">
         <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="T12" t="n">
         <v>3.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
         <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
         <v>3.44</v>
@@ -1906,13 +1906,13 @@
         <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AH12" t="n">
         <v>1.42</v>
@@ -1989,10 +1989,10 @@
         <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
         <v>1.38</v>
@@ -2007,10 +2007,10 @@
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.39</v>
+        <v>3.22</v>
       </c>
       <c r="AA13" t="n">
         <v>1.98</v>
@@ -2025,16 +2025,16 @@
         <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>2.65</v>
+        <v>2.08</v>
       </c>
       <c r="O14" t="n">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="V14" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.88</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="N15" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V15" t="n">
         <v>4.4</v>
       </c>
-      <c r="O15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="R15" t="n">
+      <c r="W15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.4</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>2.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.34</v>
+        <v>2.09</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>1.86</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>2.28</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.04</v>
+        <v>2.96</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.45</v>
+        <v>1.67</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>2.08</v>
+        <v>5.4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.85</v>
+        <v>2.39</v>
       </c>
       <c r="P16" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.33</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.34</v>
+        <v>2.1</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="M17" t="n">
-        <v>5.25</v>
+        <v>3.85</v>
       </c>
       <c r="N17" t="n">
-        <v>6.97</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.62</v>
+        <v>2.23</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>3.94</v>
       </c>
       <c r="R17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.21</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Z17" t="n">
-        <v>5.8</v>
+        <v>4.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.09</v>
+        <v>2.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.86</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.96</v>
+        <v>1.72</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>5.4</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
-        <v>2.39</v>
+        <v>3.74</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="R18" t="n">
         <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.67</v>
+        <v>3.06</v>
       </c>
       <c r="T18" t="n">
-        <v>3.18</v>
+        <v>2.85</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P19" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.94</v>
+        <v>4.95</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
       <c r="W19" t="n">
         <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.27</v>
+        <v>1.87</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.3</v>
+        <v>2.26</v>
       </c>
       <c r="M20" t="n">
-        <v>4.8</v>
+        <v>2.91</v>
       </c>
       <c r="N20" t="n">
-        <v>1.38</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>6.5</v>
+        <v>3.05</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>2.61</v>
       </c>
       <c r="T20" t="n">
-        <v>2.23</v>
+        <v>3.15</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>5.25</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>2.73</v>
       </c>
       <c r="AA20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.09</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="M21" t="n">
-        <v>2.91</v>
+        <v>3.11</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="O21" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="T21" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V21" t="n">
-        <v>9.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.13</v>
+        <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.11</v>
+        <v>4.8</v>
       </c>
       <c r="N22" t="n">
-        <v>3.59</v>
+        <v>1.38</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.98</v>
+        <v>1.86</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>3.24</v>
       </c>
       <c r="T22" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="V22" t="n">
-        <v>8.5</v>
+        <v>5.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.66</v>
+        <v>4.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.19</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3286,40 +3286,40 @@
         <v>2.35</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA24" t="n">
         <v>2.15</v>
@@ -3328,22 +3328,22 @@
         <v>1.63</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46029.70833333334</v>

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,31 +1849,31 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.69</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
-        <v>3.41</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.47</v>
+        <v>7.4</v>
       </c>
       <c r="O12" t="n">
-        <v>3.58</v>
+        <v>1.9</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.95</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="T12" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
         <v>1.38</v>
@@ -1882,40 +1882,40 @@
         <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.44</v>
+        <v>3.22</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="AD12" t="n">
         <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.42</v>
+        <v>3.1</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>2.69</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4</v>
+        <v>3.41</v>
       </c>
       <c r="N13" t="n">
-        <v>7.4</v>
+        <v>2.47</v>
       </c>
       <c r="O13" t="n">
-        <v>1.9</v>
+        <v>3.58</v>
       </c>
       <c r="P13" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>2.95</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>3.01</v>
       </c>
       <c r="U13" t="n">
         <v>1.38</v>
@@ -2001,40 +2001,40 @@
         <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD13" t="n">
         <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.52</v>
+        <v>2.02</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.1</v>
+        <v>1.42</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M14" t="n">
         <v>3.45</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.55</v>
-      </c>
       <c r="N14" t="n">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="O14" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="P14" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="M15" t="n">
-        <v>5.25</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>6.97</v>
+        <v>5.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.84</v>
+        <v>2.39</v>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9</v>
+        <v>2.67</v>
       </c>
       <c r="T15" t="n">
-        <v>2.06</v>
+        <v>3.18</v>
       </c>
       <c r="U15" t="n">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.95</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.09</v>
+        <v>3.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.86</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.96</v>
+        <v>2.1</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>3.18</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.56</v>
+        <v>3.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.13</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>5.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>6.97</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="P17" t="n">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.94</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="S17" t="n">
-        <v>3.24</v>
+        <v>3.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="V17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z17" t="n">
         <v>5.8</v>
       </c>
-      <c r="W17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.25</v>
-      </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.15</v>
+        <v>2.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.9</v>
+        <v>2.09</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.35</v>
+        <v>1.86</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.72</v>
+        <v>2.96</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="O18" t="n">
-        <v>3.74</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.7</v>
+        <v>3.94</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>3.06</v>
+        <v>3.24</v>
       </c>
       <c r="T18" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="V18" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.39</v>
+        <v>1.72</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.88</v>
+        <v>3.45</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>2.08</v>
       </c>
       <c r="O19" t="n">
-        <v>2.45</v>
+        <v>3.85</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.95</v>
+        <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="T19" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="V19" t="n">
-        <v>7.3</v>
+        <v>5.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.14</v>
+        <v>4.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.34</v>
+        <v>3.02</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.04</v>
+        <v>1.34</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46029.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46029.70833333334</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>1.66</v>
       </c>
       <c r="M25" t="n">
         <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>1.73</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>5.15</v>
+        <v>2.29</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.15</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
         <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="T25" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V25" t="n">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.98</v>
+        <v>3.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46029.71875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.66</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
         <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>1.73</v>
       </c>
       <c r="O26" t="n">
-        <v>2.29</v>
+        <v>5.15</v>
       </c>
       <c r="P26" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>2.15</v>
       </c>
       <c r="R26" t="n">
         <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="U26" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46029.71875</v>

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -642,72 +642,72 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3.59</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.56</v>
+        <v>5.79</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="T2" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
         <v>3.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC2" t="n">
         <v>3.2</v>
@@ -716,16 +716,16 @@
         <v>1.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46029.41319444445</v>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -774,32 +774,32 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="M3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="O3" t="n">
-        <v>5.47</v>
+        <v>5.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="T3" t="n">
         <v>2.59</v>
@@ -808,7 +808,7 @@
         <v>1.41</v>
       </c>
       <c r="V3" t="n">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="W3" t="n">
         <v>1.06</v>
@@ -826,25 +826,25 @@
         <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
         <v>2.83</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AF3" t="n">
         <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46029.41666666666</v>
@@ -906,64 +906,64 @@
         <v>1.88</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA4" t="n">
         <v>2.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46029.47222222222</v>
@@ -1025,13 +1025,13 @@
         <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>3.51</v>
+        <v>3.36</v>
       </c>
       <c r="P5" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
@@ -1046,7 +1046,7 @@
         <v>1.52</v>
       </c>
       <c r="V5" t="n">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="W5" t="n">
         <v>1.09</v>
@@ -1055,10 +1055,10 @@
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AA5" t="n">
         <v>1.55</v>
@@ -1073,16 +1073,16 @@
         <v>1.55</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AG5" t="n">
         <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46029.47916666666</v>
@@ -1144,10 +1144,10 @@
         <v>1.68</v>
       </c>
       <c r="O6" t="n">
-        <v>5.64</v>
+        <v>5.92</v>
       </c>
       <c r="P6" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
         <v>2.34</v>
@@ -1156,28 +1156,28 @@
         <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>7.7</v>
+        <v>9.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="AA6" t="n">
         <v>2.13</v>
@@ -1186,22 +1186,22 @@
         <v>1.64</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.96</v>
+        <v>4.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
         <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46029.48263888889</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>9.5</v>
+        <v>6.4</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7</v>
+        <v>4.35</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="O7" t="n">
         <v>6.25</v>
@@ -1269,22 +1269,22 @@
         <v>2.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V7" t="n">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="W7" t="n">
         <v>1.08</v>
@@ -1296,31 +1296,31 @@
         <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46029.53125</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="N8" t="n">
         <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="P8" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.6</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="T8" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="U8" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.05</v>
+        <v>3.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.49</v>
+        <v>2.97</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.41</v>
+        <v>2.71</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.95</v>
+        <v>3.78</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46029.53819444445</v>
@@ -1623,10 +1623,10 @@
         <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R10" t="n">
         <v>1.16</v>
@@ -1638,22 +1638,22 @@
         <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V10" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.7</v>
+        <v>6.83</v>
       </c>
       <c r="AA10" t="n">
         <v>1.35</v>
@@ -1668,10 +1668,10 @@
         <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF10" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="AG10" t="n">
         <v>1.22</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,31 +1849,31 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.41</v>
+        <v>2.69</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4</v>
+        <v>3.41</v>
       </c>
       <c r="N12" t="n">
-        <v>7.4</v>
+        <v>2.47</v>
       </c>
       <c r="O12" t="n">
-        <v>1.9</v>
+        <v>3.35</v>
       </c>
       <c r="P12" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>2.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="U12" t="n">
         <v>1.38</v>
@@ -1882,40 +1882,40 @@
         <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.22</v>
+        <v>3.64</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
         <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.52</v>
+        <v>2.02</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.1</v>
+        <v>1.42</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,37 +1968,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.69</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>3.41</v>
+        <v>4.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.47</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.58</v>
+        <v>1.95</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="T13" t="n">
-        <v>3.01</v>
+        <v>3.29</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
@@ -2007,34 +2007,34 @@
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="AD13" t="n">
         <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.72</v>
+        <v>2.52</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.02</v>
+        <v>1.47</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.42</v>
+        <v>3.14</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.74</v>
+        <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>3.77</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="V14" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.35</v>
+        <v>2.82</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.39</v>
+        <v>1.72</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
-        <v>5.4</v>
+        <v>6.32</v>
       </c>
       <c r="O15" t="n">
-        <v>2.39</v>
+        <v>1.9</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="Q15" t="n">
         <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>2.67</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>3.18</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z15" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>1.37</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>2.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.56</v>
+        <v>2.07</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.97</v>
+        <v>1.52</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.1</v>
+        <v>2.77</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>2.65</v>
       </c>
       <c r="O16" t="n">
-        <v>2.45</v>
+        <v>3.62</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.95</v>
+        <v>2.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="T16" t="n">
         <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>7.3</v>
+        <v>6.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.04</v>
+        <v>1.42</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="M17" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>6.97</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>3.9</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>2.06</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.09</v>
+        <v>3.74</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.86</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.28</v>
+        <v>1.78</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.96</v>
+        <v>1.99</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z18" t="n">
         <v>3.1</v>
       </c>
-      <c r="O18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z18" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2691,7 +2691,7 @@
         <v>2.08</v>
       </c>
       <c r="O19" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P19" t="n">
         <v>2.24</v>
@@ -2700,10 +2700,10 @@
         <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>3.12</v>
+        <v>3.31</v>
       </c>
       <c r="T19" t="n">
         <v>2.5</v>
@@ -2712,7 +2712,7 @@
         <v>1.46</v>
       </c>
       <c r="V19" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
         <v>1.08</v>
@@ -2724,7 +2724,7 @@
         <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AA19" t="n">
         <v>1.8</v>
@@ -2733,19 +2733,19 @@
         <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE19" t="n">
         <v>1.68</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
         <v>1.34</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="M20" t="n">
-        <v>2.91</v>
+        <v>3.11</v>
       </c>
       <c r="N20" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="O20" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.13</v>
+        <v>7.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.11</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
-        <v>3.59</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="P21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE21" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V21" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD21" t="n">
+      <c r="AF21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.19</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7.3</v>
+        <v>2.26</v>
       </c>
       <c r="M22" t="n">
-        <v>4.8</v>
+        <v>2.91</v>
       </c>
       <c r="N22" t="n">
-        <v>1.38</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
-        <v>6.5</v>
+        <v>3.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.86</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="S22" t="n">
-        <v>3.24</v>
+        <v>2.61</v>
       </c>
       <c r="T22" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
-        <v>5.4</v>
+        <v>10.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.2</v>
+        <v>2.66</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AF22" t="n">
         <v>1.82</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.09</v>
+        <v>1.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46029.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46029.70833333334</v>
@@ -3405,28 +3405,28 @@
         <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="P25" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="Q25" t="n">
         <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
         <v>2.98</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="U25" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="W25" t="n">
         <v>1.09</v>
@@ -3435,34 +3435,34 @@
         <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AC25" t="n">
         <v>2.84</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46029.71875</v>
@@ -3524,40 +3524,40 @@
         <v>1.73</v>
       </c>
       <c r="O26" t="n">
-        <v>5.15</v>
+        <v>5.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="T26" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
-        <v>6.15</v>
+        <v>6.6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="AA26" t="n">
         <v>1.7</v>
@@ -3566,19 +3566,19 @@
         <v>2.15</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="n">
         <v>1.2</v>

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -999,20 +999,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1121,17 +1121,17 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1240,17 +1240,17 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1475,30 +1475,30 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="M9" t="n">
-        <v>2.99</v>
+        <v>2.71</v>
       </c>
       <c r="N9" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>2.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="M10" t="n">
         <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="Q10" t="n">
         <v>2.64</v>
@@ -1635,16 +1635,16 @@
         <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U10" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
@@ -1653,31 +1653,31 @@
         <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.83</v>
+        <v>6.79</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46029.5625</v>
@@ -1713,30 +1713,30 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="M11" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>4.33</v>
+        <v>4.17</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.69</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>3.41</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.47</v>
+        <v>11.64</v>
       </c>
       <c r="O12" t="n">
-        <v>3.35</v>
+        <v>1.86</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.95</v>
+        <v>10.73</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.89</v>
+        <v>2.19</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="AD12" t="n">
         <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.72</v>
+        <v>2.58</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.02</v>
+        <v>1.45</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.42</v>
+        <v>3.3</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,37 +1968,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>2.9</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>7.4</v>
+        <v>2.23</v>
       </c>
       <c r="O13" t="n">
-        <v>1.95</v>
+        <v>3.66</v>
       </c>
       <c r="P13" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="T13" t="n">
-        <v>3.29</v>
+        <v>2.95</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
@@ -2007,34 +2007,34 @@
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="AD13" t="n">
         <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.52</v>
+        <v>1.72</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.47</v>
+        <v>2.09</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.14</v>
+        <v>1.42</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.77</v>
+        <v>4.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.25</v>
+        <v>2.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.82</v>
+        <v>3.74</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="M15" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>6.32</v>
+        <v>5.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.9</v>
+        <v>2.43</v>
       </c>
       <c r="P15" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>2.06</v>
+        <v>3.19</v>
       </c>
       <c r="U15" t="n">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.37</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.95</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.07</v>
+        <v>3.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.87</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.52</v>
+        <v>1.98</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
         <v>1.21</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.77</v>
+        <v>2.07</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N16" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
-        <v>3.62</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.75</v>
+        <v>3.77</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="V16" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>2.65</v>
       </c>
       <c r="O17" t="n">
-        <v>2.4</v>
+        <v>3.62</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.42</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.74</v>
+        <v>3.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.99</v>
+        <v>1.42</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>5.4</v>
+        <v>6.32</v>
       </c>
       <c r="O18" t="n">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>3.19</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="W18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.07</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z18" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>1.37</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.77</v>
+        <v>2.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.56</v>
+        <v>2.07</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.98</v>
+        <v>1.52</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AG18" t="n">
         <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.07</v>
+        <v>2.77</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2801,40 +2801,40 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="M20" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.59</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
         <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="R20" t="n">
         <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="T20" t="n">
         <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
         <v>1.07</v>
@@ -2846,10 +2846,10 @@
         <v>2.66</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC20" t="n">
         <v>4.1</v>
@@ -2858,16 +2858,16 @@
         <v>1.19</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AF20" t="n">
         <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46029.69791666666</v>
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="M21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="O21" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="R21" t="n">
         <v>1.3</v>
@@ -2944,31 +2944,31 @@
         <v>3.24</v>
       </c>
       <c r="T21" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
         <v>1.51</v>
       </c>
       <c r="V21" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="W21" t="n">
         <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
         <v>2.56</v>
@@ -2977,13 +2977,13 @@
         <v>1.48</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
         <v>1.08</v>
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
         <v>3.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q22" t="n">
         <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S22" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V22" t="n">
         <v>10.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
         <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.66</v>
+        <v>2.89</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AC22" t="n">
         <v>4.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
         <v>1.42</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46029.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46029.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46029.70833333334</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.66</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
         <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>1.73</v>
       </c>
       <c r="O25" t="n">
-        <v>2.22</v>
+        <v>5.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="T25" t="n">
-        <v>2.67</v>
+        <v>2.48</v>
       </c>
       <c r="U25" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.81</v>
       </c>
-      <c r="AB25" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF25" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.29</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.24</v>
+        <v>1.2</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46029.71875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>1.66</v>
       </c>
       <c r="M26" t="n">
         <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>1.73</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>5.3</v>
+        <v>2.22</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.36</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y26" t="n">
+      <c r="AE26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.2</v>
+        <v>2.24</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46029.71875</v>

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1832,20 +1832,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1954,17 +1954,17 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.88</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
         <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>1.85</v>
       </c>
       <c r="O14" t="n">
-        <v>2.4</v>
+        <v>4.05</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>2.65</v>
+        <v>3.24</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.88</v>
+        <v>4.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.74</v>
+        <v>2.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.99</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>5.4</v>
+        <v>4.74</v>
       </c>
       <c r="O15" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
         <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
-        <v>3.19</v>
+        <v>3.01</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.07</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.13</v>
+        <v>1.51</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>6.11</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.77</v>
+        <v>5.52</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.45</v>
+        <v>2.04</v>
       </c>
       <c r="U16" t="n">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="V16" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="W16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.07</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Z16" t="n">
-        <v>4.25</v>
+        <v>5.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.82</v>
+        <v>2.03</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.37</v>
+        <v>1.76</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.72</v>
+        <v>2.67</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="M17" t="n">
         <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>3.62</v>
+        <v>2.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.98</v>
+        <v>2.71</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>2.31</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.63</v>
+        <v>2.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.46</v>
+        <v>2.9</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>6.32</v>
+        <v>2.28</v>
       </c>
       <c r="O18" t="n">
-        <v>1.9</v>
+        <v>3.49</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9</v>
+        <v>3.01</v>
       </c>
       <c r="T18" t="n">
-        <v>2.06</v>
+        <v>2.97</v>
       </c>
       <c r="U18" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="V18" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.8</v>
+        <v>3.34</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.37</v>
       </c>
-      <c r="AB18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2.77</v>
+        <v>1.41</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.45</v>
+        <v>2.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.08</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.5</v>
+        <v>3.91</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V19" t="n">
         <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.97</v>
+        <v>2.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.34</v>
+        <v>1.74</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.11</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.99</v>
+        <v>1.76</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="T23" t="n">
-        <v>3.2</v>
+        <v>2.53</v>
       </c>
       <c r="U23" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.05</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.28</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46029.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46029.70833333334</v>
@@ -3396,16 +3396,16 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="N25" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="O25" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="P25" t="n">
         <v>2.2</v>
@@ -3420,13 +3420,13 @@
         <v>2.88</v>
       </c>
       <c r="T25" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="U25" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V25" t="n">
-        <v>6.6</v>
+        <v>6.25</v>
       </c>
       <c r="W25" t="n">
         <v>1.06</v>
@@ -3435,31 +3435,31 @@
         <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
         <v>1.2</v>
@@ -3518,70 +3518,70 @@
         <v>1.66</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="P26" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="Q26" t="n">
         <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
         <v>2.98</v>
       </c>
       <c r="T26" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="U26" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V26" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="W26" t="n">
         <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AC26" t="n">
         <v>2.84</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46029.71875</v>

--- a/jogos_2026-01-07.xlsx
+++ b/jogos_2026-01-07.xlsx
@@ -1823,16 +1823,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>2</v>
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>2.9</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>11.64</v>
+        <v>2.23</v>
       </c>
       <c r="O12" t="n">
-        <v>1.86</v>
+        <v>3.66</v>
       </c>
       <c r="P12" t="n">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.73</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="W12" t="n">
         <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z12" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
         <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.58</v>
+        <v>1.72</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.45</v>
+        <v>2.09</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.3</v>
+        <v>1.42</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46029.60416666666</v>
@@ -1942,16 +1942,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
@@ -1960,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.9</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2.23</v>
+        <v>11.64</v>
       </c>
       <c r="O13" t="n">
-        <v>3.66</v>
+        <v>1.86</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>10.73</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="T13" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="AD13" t="n">
         <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.72</v>
+        <v>2.58</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.09</v>
+        <v>1.45</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.42</v>
+        <v>3.3</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46029.60416666666</v>
@@ -2061,99 +2061,99 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC14" t="n">
         <v>3.4</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="AD14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.85</v>
       </c>
-      <c r="O14" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>2.05</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46029.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2202,77 +2202,77 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>4.74</v>
+        <v>2.28</v>
       </c>
       <c r="O15" t="n">
-        <v>2.42</v>
+        <v>3.49</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
         <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="T15" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
         <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.05</v>
+        <v>1.41</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46029.6875</v>
@@ -2299,99 +2299,99 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="M16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N16" t="n">
         <v>4.6</v>
       </c>
-      <c r="N16" t="n">
-        <v>6.11</v>
-      </c>
       <c r="O16" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.52</v>
+        <v>4.75</v>
       </c>
       <c r="R16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V16" t="n">
+        <v>9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.2</v>
       </c>
-      <c r="S16" t="n">
-        <v>4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46029.6875</v>
@@ -2418,99 +2418,99 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>6.11</v>
       </c>
       <c r="O17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2.4</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V17" t="n">
-        <v>9</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46029.6875</v>
@@ -2537,99 +2537,99 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.28</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
-        <v>3.49</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
         <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>3.91</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="U18" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.35</v>
+        <v>2.82</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46029.6875</v>
@@ -2656,19 +2656,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>1.85</v>
       </c>
       <c r="O19" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2.5</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.91</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="T19" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.2</v>
       </c>
-      <c r="AC19" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.74</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46029.6875</v>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -2906,17 +2906,17 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3263,17 +3263,17 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3379,20 +3379,20 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3498,20 +3498,20 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
